--- a/dados_excel/tournaments.xlsx
+++ b/dados_excel/tournaments.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="tournaments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tournaments" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -728,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1108,6 +1108,32 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Classificatória 4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AcadArena</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>46277.54166666666</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>46278.95833333334</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>assets/tournament-icons/UNIVAVA.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
